--- a/artfynd/A 59137-2024 artfynd.xlsx
+++ b/artfynd/A 59137-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,6 +1015,524 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121635270</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Slogmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>564082</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6698553</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121635267</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Slogmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>564145</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6698572</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121635264</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56568</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Slogmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>563952</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6698330</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121635262</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Slogmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>563981</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6698547</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121635269</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Slogmossen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>563991</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6698556</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59137-2024 artfynd.xlsx
+++ b/artfynd/A 59137-2024 artfynd.xlsx
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121635270</v>
+        <v>121635267</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564082</v>
+        <v>564145</v>
       </c>
       <c r="R5" t="n">
-        <v>6698553</v>
+        <v>6698572</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121635267</v>
+        <v>121635270</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564145</v>
+        <v>564082</v>
       </c>
       <c r="R6" t="n">
-        <v>6698572</v>
+        <v>6698553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121635264</v>
+        <v>121635262</v>
       </c>
       <c r="B7" t="n">
-        <v>56568</v>
+        <v>90728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,46 +1233,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563952</v>
+        <v>563981</v>
       </c>
       <c r="R7" t="n">
-        <v>6698330</v>
+        <v>6698547</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121635262</v>
+        <v>121635264</v>
       </c>
       <c r="B8" t="n">
-        <v>90720</v>
+        <v>56569</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,38 +1335,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563981</v>
+        <v>563952</v>
       </c>
       <c r="R8" t="n">
-        <v>6698547</v>
+        <v>6698330</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1436,7 @@
         <v>121635269</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 59137-2024 artfynd.xlsx
+++ b/artfynd/A 59137-2024 artfynd.xlsx
@@ -1017,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121635267</v>
+        <v>121635270</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564145</v>
+        <v>564082</v>
       </c>
       <c r="R5" t="n">
-        <v>6698572</v>
+        <v>6698553</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121635262</v>
+        <v>121635269</v>
       </c>
       <c r="B6" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563981</v>
+        <v>563991</v>
       </c>
       <c r="R6" t="n">
-        <v>6698547</v>
+        <v>6698556</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121635264</v>
+        <v>121635262</v>
       </c>
       <c r="B7" t="n">
-        <v>56569</v>
+        <v>90728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,46 +1233,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563952</v>
+        <v>563981</v>
       </c>
       <c r="R7" t="n">
-        <v>6698330</v>
+        <v>6698547</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,7 +1323,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121635270</v>
+        <v>121635267</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1371,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564082</v>
+        <v>564145</v>
       </c>
       <c r="R8" t="n">
-        <v>6698553</v>
+        <v>6698572</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121635269</v>
+        <v>121635264</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>56569</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,38 +1437,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563991</v>
+        <v>563952</v>
       </c>
       <c r="R9" t="n">
-        <v>6698556</v>
+        <v>6698330</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 59137-2024 artfynd.xlsx
+++ b/artfynd/A 59137-2024 artfynd.xlsx
@@ -1323,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121635267</v>
+        <v>121635264</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>56569</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,38 +1335,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564145</v>
+        <v>563952</v>
       </c>
       <c r="R8" t="n">
-        <v>6698572</v>
+        <v>6698330</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121635264</v>
+        <v>121635267</v>
       </c>
       <c r="B9" t="n">
-        <v>56569</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,46 +1445,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563952</v>
+        <v>564145</v>
       </c>
       <c r="R9" t="n">
-        <v>6698330</v>
+        <v>6698572</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 59137-2024 artfynd.xlsx
+++ b/artfynd/A 59137-2024 artfynd.xlsx
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121635270</v>
+        <v>121635262</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564082</v>
+        <v>563981</v>
       </c>
       <c r="R5" t="n">
-        <v>6698553</v>
+        <v>6698547</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121635262</v>
+        <v>121635270</v>
       </c>
       <c r="B7" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,21 +1237,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563981</v>
+        <v>564082</v>
       </c>
       <c r="R7" t="n">
-        <v>6698547</v>
+        <v>6698553</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 59137-2024 artfynd.xlsx
+++ b/artfynd/A 59137-2024 artfynd.xlsx
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121635269</v>
+        <v>121635270</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563991</v>
+        <v>564082</v>
       </c>
       <c r="R6" t="n">
-        <v>6698556</v>
+        <v>6698553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1221,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121635270</v>
+        <v>121635267</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564082</v>
+        <v>564145</v>
       </c>
       <c r="R7" t="n">
-        <v>6698553</v>
+        <v>6698572</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121635264</v>
+        <v>121635269</v>
       </c>
       <c r="B8" t="n">
-        <v>56569</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,46 +1335,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563952</v>
+        <v>563991</v>
       </c>
       <c r="R8" t="n">
-        <v>6698330</v>
+        <v>6698556</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1433,10 +1425,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121635267</v>
+        <v>121635264</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>56569</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,38 +1437,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564145</v>
+        <v>563952</v>
       </c>
       <c r="R9" t="n">
-        <v>6698572</v>
+        <v>6698330</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 59137-2024 artfynd.xlsx
+++ b/artfynd/A 59137-2024 artfynd.xlsx
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121635262</v>
+        <v>121635269</v>
       </c>
       <c r="B5" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563981</v>
+        <v>563991</v>
       </c>
       <c r="R5" t="n">
-        <v>6698547</v>
+        <v>6698556</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121635270</v>
+        <v>121635267</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564082</v>
+        <v>564145</v>
       </c>
       <c r="R6" t="n">
-        <v>6698553</v>
+        <v>6698572</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121635267</v>
+        <v>121635262</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,21 +1237,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564145</v>
+        <v>563981</v>
       </c>
       <c r="R7" t="n">
-        <v>6698572</v>
+        <v>6698547</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1323,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121635269</v>
+        <v>121635270</v>
       </c>
       <c r="B8" t="n">
         <v>78616</v>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563991</v>
+        <v>564082</v>
       </c>
       <c r="R8" t="n">
-        <v>6698556</v>
+        <v>6698553</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 59137-2024 artfynd.xlsx
+++ b/artfynd/A 59137-2024 artfynd.xlsx
@@ -1017,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121635269</v>
+        <v>121635270</v>
       </c>
       <c r="B5" t="n">
         <v>78616</v>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563991</v>
+        <v>564082</v>
       </c>
       <c r="R5" t="n">
-        <v>6698556</v>
+        <v>6698553</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121635267</v>
+        <v>121635269</v>
       </c>
       <c r="B6" t="n">
         <v>78616</v>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564145</v>
+        <v>563991</v>
       </c>
       <c r="R6" t="n">
-        <v>6698572</v>
+        <v>6698556</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121635262</v>
+        <v>121635267</v>
       </c>
       <c r="B7" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,21 +1237,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563981</v>
+        <v>564145</v>
       </c>
       <c r="R7" t="n">
-        <v>6698547</v>
+        <v>6698572</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121635270</v>
+        <v>121635262</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,21 +1339,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564082</v>
+        <v>563981</v>
       </c>
       <c r="R8" t="n">
-        <v>6698553</v>
+        <v>6698547</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 59137-2024 artfynd.xlsx
+++ b/artfynd/A 59137-2024 artfynd.xlsx
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121635270</v>
+        <v>121635264</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>56577</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,38 +1029,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564082</v>
+        <v>563952</v>
       </c>
       <c r="R5" t="n">
-        <v>6698553</v>
+        <v>6698330</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121635269</v>
+        <v>121635267</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,10 +1167,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563991</v>
+        <v>564145</v>
       </c>
       <c r="R6" t="n">
-        <v>6698556</v>
+        <v>6698572</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121635267</v>
+        <v>121635262</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>90742</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564145</v>
+        <v>563981</v>
       </c>
       <c r="R7" t="n">
-        <v>6698572</v>
+        <v>6698547</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121635262</v>
+        <v>121635270</v>
       </c>
       <c r="B8" t="n">
-        <v>90728</v>
+        <v>78629</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1363,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563981</v>
+        <v>564082</v>
       </c>
       <c r="R8" t="n">
-        <v>6698547</v>
+        <v>6698553</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121635264</v>
+        <v>121635269</v>
       </c>
       <c r="B9" t="n">
-        <v>56569</v>
+        <v>78629</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,46 +1445,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563952</v>
+        <v>563991</v>
       </c>
       <c r="R9" t="n">
-        <v>6698330</v>
+        <v>6698556</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 59137-2024 artfynd.xlsx
+++ b/artfynd/A 59137-2024 artfynd.xlsx
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121635264</v>
+        <v>121635270</v>
       </c>
       <c r="B5" t="n">
-        <v>56577</v>
+        <v>78631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,46 +1029,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563952</v>
+        <v>564082</v>
       </c>
       <c r="R5" t="n">
-        <v>6698330</v>
+        <v>6698553</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121635267</v>
+        <v>121635264</v>
       </c>
       <c r="B6" t="n">
-        <v>78629</v>
+        <v>56577</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,38 +1131,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564145</v>
+        <v>563952</v>
       </c>
       <c r="R6" t="n">
-        <v>6698572</v>
+        <v>6698330</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121635262</v>
+        <v>121635267</v>
       </c>
       <c r="B7" t="n">
-        <v>90742</v>
+        <v>78631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1269,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563981</v>
+        <v>564145</v>
       </c>
       <c r="R7" t="n">
-        <v>6698547</v>
+        <v>6698572</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121635270</v>
+        <v>121635262</v>
       </c>
       <c r="B8" t="n">
-        <v>78629</v>
+        <v>90744</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564082</v>
+        <v>563981</v>
       </c>
       <c r="R8" t="n">
-        <v>6698553</v>
+        <v>6698547</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1436,7 @@
         <v>121635269</v>
       </c>
       <c r="B9" t="n">
-        <v>78629</v>
+        <v>78631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 59137-2024 artfynd.xlsx
+++ b/artfynd/A 59137-2024 artfynd.xlsx
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121635270</v>
+        <v>121635262</v>
       </c>
       <c r="B5" t="n">
-        <v>78631</v>
+        <v>90745</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564082</v>
+        <v>563981</v>
       </c>
       <c r="R5" t="n">
-        <v>6698553</v>
+        <v>6698547</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121635264</v>
+        <v>121635270</v>
       </c>
       <c r="B6" t="n">
-        <v>56577</v>
+        <v>78632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,46 +1131,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563952</v>
+        <v>564082</v>
       </c>
       <c r="R6" t="n">
-        <v>6698330</v>
+        <v>6698553</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1229,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121635267</v>
+        <v>121635264</v>
       </c>
       <c r="B7" t="n">
-        <v>78631</v>
+        <v>56577</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,38 +1233,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Slogmossen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564145</v>
+        <v>563952</v>
       </c>
       <c r="R7" t="n">
-        <v>6698572</v>
+        <v>6698330</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121635262</v>
+        <v>121635267</v>
       </c>
       <c r="B8" t="n">
-        <v>90744</v>
+        <v>78632</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563981</v>
+        <v>564145</v>
       </c>
       <c r="R8" t="n">
-        <v>6698547</v>
+        <v>6698572</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1436,7 @@
         <v>121635269</v>
       </c>
       <c r="B9" t="n">
-        <v>78631</v>
+        <v>78632</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
